--- a/data/FWC26_TX_Input_v3.xlsx
+++ b/data/FWC26_TX_Input_v3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HBMC Op 01\.vscode\hbs-tx-schedule\hbs-tx-schedule\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HBMC Op 01\.vscode\hbs-tx-schedule\hbs-tx-schedule\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61D61FF-DDB2-40FA-B3AE-1431CD777D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B14BB8-CE54-4CF5-85E2-BACFAD3989C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2904" windowWidth="23040" windowHeight="12120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="2904" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Services" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="342">
   <si>
     <t>SERVICES — Start offset: min from KO. Stop offset: min from Final Whistle (FW = KO + match_duration_min). Negative stop = before FW; positive = after FW.</t>
   </si>
@@ -1555,7 +1555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -1667,32 +1667,38 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>-90</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="C9">
+        <v>-90</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10">
         <v>-90</v>
@@ -1703,7 +1709,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
@@ -1717,24 +1723,24 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12">
-        <v>-90</v>
+        <v>-120</v>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>-90</v>
@@ -1745,24 +1751,24 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14">
-        <v>-120</v>
+        <v>-60</v>
       </c>
       <c r="D14">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>-90</v>
@@ -1776,13 +1782,13 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16">
         <v>-60</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1790,13 +1796,19 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C17">
-        <v>-90</v>
+        <v>-10</v>
       </c>
       <c r="D17">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1804,13 +1816,19 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C18">
-        <v>-60</v>
+        <v>-10</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1818,19 +1836,13 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C19">
-        <v>-10</v>
+        <v>-120</v>
       </c>
       <c r="D19">
-        <v>10</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1838,19 +1850,13 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C20">
-        <v>-10</v>
+        <v>-150</v>
       </c>
       <c r="D20">
-        <v>10</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1858,13 +1864,13 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>-120</v>
+        <v>-150</v>
       </c>
       <c r="D21">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1872,13 +1878,13 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22">
+        <v>-30</v>
+      </c>
+      <c r="D22">
         <v>20</v>
-      </c>
-      <c r="C22">
-        <v>-150</v>
-      </c>
-      <c r="D22">
-        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1886,41 +1892,41 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C23">
-        <v>-150</v>
+        <v>-70</v>
       </c>
       <c r="D23">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>-30</v>
+        <v>-150</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C25">
-        <v>-70</v>
+        <v>-150</v>
       </c>
       <c r="D25">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1928,13 +1934,13 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C26">
-        <v>-150</v>
+        <v>-120</v>
       </c>
       <c r="D26">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1942,13 +1948,13 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C27">
-        <v>-150</v>
+        <v>-90</v>
       </c>
       <c r="D27">
-        <v>65</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1956,13 +1962,10 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28">
-        <v>-120</v>
-      </c>
-      <c r="D28">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1970,48 +1973,23 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29">
-        <v>-90</v>
-      </c>
-      <c r="D29">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" t="s">
         <v>23</v>
       </c>
-      <c r="C32">
+      <c r="C30">
         <v>-90</v>
       </c>
-      <c r="D32">
+      <c r="D30">
         <v>15</v>
       </c>
     </row>

--- a/data/FWC26_TX_Input_v3.xlsx
+++ b/data/FWC26_TX_Input_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HBMC Op 01\.vscode\hbs-tx-schedule\hbs-tx-schedule\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14E530B-E294-47D6-A62F-077657874BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC411331-D1C8-411A-8785-B316C83D3A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32196" yWindow="1356" windowWidth="23040" windowHeight="13068" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -259,7 +259,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,14 +279,8 @@
       <color rgb="FF8BC34A"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF7B9FE0"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,11 +297,6 @@
         <fgColor rgb="FF1A2E0A"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A1E35"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -321,13 +310,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -780,7 +768,7 @@
         <v>65</v>
       </c>
       <c r="D3">
-        <v>-90</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -788,7 +776,7 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>-90</v>
+        <v>-105</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -802,7 +790,7 @@
         <v>28</v>
       </c>
       <c r="B5">
-        <v>-45</v>
+        <v>-50</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -819,7 +807,7 @@
         <v>30</v>
       </c>
       <c r="B6">
-        <v>-45</v>
+        <v>-75</v>
       </c>
       <c r="C6">
         <v>60</v>
@@ -836,7 +824,7 @@
         <v>32</v>
       </c>
       <c r="B7">
-        <v>-45</v>
+        <v>-55</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -853,10 +841,10 @@
         <v>-185</v>
       </c>
       <c r="C8">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="D8">
-        <v>-60</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -864,7 +852,7 @@
         <v>34</v>
       </c>
       <c r="B9">
-        <v>-150</v>
+        <v>-155</v>
       </c>
       <c r="C9">
         <v>65</v>
@@ -878,7 +866,7 @@
         <v>35</v>
       </c>
       <c r="B10">
-        <v>-90</v>
+        <v>-110</v>
       </c>
       <c r="C10">
         <v>15</v>
@@ -1361,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -1460,7 +1448,7 @@
         <v>64</v>
       </c>
       <c r="D7">
-        <v>-60</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1476,20 +1464,6 @@
       <c r="D8">
         <v>-45</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
